--- a/棚卸match.xlsx
+++ b/棚卸match.xlsx
@@ -1,20 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k-yakuzai\Desktop\坂下\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_9540F315367003803597FD01EBF4952BA5269322" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="match_results_top5_260317" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -270,7 +284,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1187,16 +1201,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q17"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="44.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="42.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="44.37890625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="42.171875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="42.171875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1249,7 +1263,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1302,7 +1316,7 @@
         <v>60.465116279069697</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1355,7 +1369,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1408,7 +1422,7 @@
         <v>63.157894736842103</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1461,7 +1475,7 @@
         <v>45.454545454545404</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1514,7 +1528,7 @@
         <v>42.105263157894697</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1567,7 +1581,7 @@
         <v>55.172413793103402</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1620,7 +1634,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1673,7 +1687,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1726,7 +1740,7 @@
         <v>31.818181818181799</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1770,7 +1784,7 @@
         <v>30.769230769230699</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1796,7 +1810,7 @@
         <v>66.6666666666666</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1822,7 +1836,7 @@
         <v>58.823529411764703</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1875,7 +1889,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1928,7 +1942,7 @@
         <v>43.243243243243199</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1972,7 +1986,7 @@
         <v>33.3333333333333</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
